--- a/experiment/ELAN_bestx2/Test/results-B100/B100.xlsx
+++ b/experiment/ELAN_bestx2/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.42</v>
+        <v>27.23</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7724</v>
+        <v>0.7999000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31.32</v>
+        <v>32.87</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9061</v>
+        <v>0.9264</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.69</v>
+        <v>30.54</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8917</v>
+        <v>0.9191</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.99</v>
+        <v>35.78</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9453</v>
+        <v>0.9603</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29.47</v>
+        <v>30.22</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8794</v>
+        <v>0.8979</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36.07</v>
+        <v>38.26</v>
       </c>
       <c r="C7" t="n">
-        <v>0.947</v>
+        <v>0.9587</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.43</v>
+        <v>32.29</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9144</v>
+        <v>0.9379999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.18</v>
+        <v>27.24</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8335</v>
+        <v>0.8641</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31.01</v>
+        <v>32.31</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9112</v>
+        <v>0.9276</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32.84</v>
+        <v>34.15</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9201</v>
+        <v>0.9358</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.08</v>
+        <v>29.96</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8599</v>
+        <v>0.9208</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.06</v>
+        <v>34.51</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.9356</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34.5</v>
+        <v>35.55</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9397</v>
+        <v>0.9513</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>31.9</v>
+        <v>34.41</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9116</v>
+        <v>0.9381</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.24</v>
+        <v>29.37</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8649</v>
+        <v>0.8914</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.36</v>
+        <v>32.33</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9142</v>
+        <v>0.9445</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>36.93</v>
+        <v>38.92</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9427</v>
+        <v>0.9578</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>35.86</v>
+        <v>37.22</v>
       </c>
       <c r="C19" t="n">
-        <v>0.946</v>
+        <v>0.9603</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27.81</v>
+        <v>29.46</v>
       </c>
       <c r="C20" t="n">
-        <v>0.845</v>
+        <v>0.8754</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28.46</v>
+        <v>30.19</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8912</v>
+        <v>0.9156</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25.35</v>
+        <v>27.3</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8521</v>
+        <v>0.9086</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27.02</v>
+        <v>29.1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8348</v>
+        <v>0.8829</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27.17</v>
+        <v>27.58</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7682</v>
+        <v>0.7901</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.43</v>
+        <v>31.32</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9099</v>
+        <v>0.9411</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.36</v>
+        <v>33.35</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9297</v>
+        <v>0.9491000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30.81</v>
+        <v>31.88</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9319</v>
+        <v>0.9441000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>31.03</v>
+        <v>32.32</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8812</v>
+        <v>0.9041</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>33.46</v>
+        <v>34.93</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9204</v>
+        <v>0.9387</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>33.18</v>
+        <v>37.64</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9378</v>
+        <v>0.9651999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.45</v>
+        <v>23.2</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7431</v>
+        <v>0.7806999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>33.56</v>
+        <v>35.35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9338</v>
+        <v>0.9485</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23.77</v>
+        <v>24.74</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7319</v>
+        <v>0.784</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29.23</v>
+        <v>30.33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8829</v>
+        <v>0.9055</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26.86</v>
+        <v>27.99</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8714</v>
+        <v>0.8986</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>36.57</v>
+        <v>39.85</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9424</v>
+        <v>0.9549</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30.09</v>
+        <v>31.72</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8792</v>
+        <v>0.9049</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29.83</v>
+        <v>30.11</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7154</v>
+        <v>0.7281</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30.36</v>
+        <v>31.36</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8431</v>
+        <v>0.8643999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>32.1</v>
+        <v>34.15</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9357</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.36</v>
+        <v>43.76</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9709</v>
+        <v>0.9883999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29.33</v>
+        <v>31.87</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8595</v>
+        <v>0.8902</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>27.97</v>
+        <v>29.83</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8439</v>
+        <v>0.8826000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29.2</v>
+        <v>31.07</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8641</v>
+        <v>0.8922</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30.62</v>
+        <v>34.21</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9454</v>
+        <v>0.9674</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27.13</v>
+        <v>29.23</v>
       </c>
       <c r="C46" t="n">
-        <v>0.8328</v>
+        <v>0.8929</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>36.74</v>
+        <v>38.55</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9286</v>
+        <v>0.9476</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>26.02</v>
+        <v>27.9</v>
       </c>
       <c r="C48" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8694</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.3</v>
+        <v>29.07</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8492</v>
+        <v>0.8709</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>30.13</v>
+        <v>34.33</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9442</v>
+        <v>0.9725</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>34.77</v>
+        <v>35.8</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9161</v>
+        <v>0.9283</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.6</v>
+        <v>28.42</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8109</v>
+        <v>0.8375</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>26.11</v>
+        <v>29.06</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8672</v>
+        <v>0.8981</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>34.73</v>
+        <v>35.68</v>
       </c>
       <c r="C54" t="n">
-        <v>0.9149</v>
+        <v>0.9268999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>35.36</v>
+        <v>36.02</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8986</v>
+        <v>0.9099</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>30.97</v>
+        <v>33.69</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9019</v>
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>28.37</v>
+        <v>30.68</v>
       </c>
       <c r="C57" t="n">
-        <v>0.8579</v>
+        <v>0.9014</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>23.74</v>
+        <v>24.37</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6997</v>
+        <v>0.7378</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>30</v>
+        <v>30.98</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8595</v>
+        <v>0.8844</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>34.73</v>
+        <v>35.2</v>
       </c>
       <c r="C60" t="n">
-        <v>0.895</v>
+        <v>0.9046999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>32.86</v>
+        <v>34.19</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8748</v>
+        <v>0.8948</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>34.15</v>
+        <v>35.09</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8962</v>
+        <v>0.9116</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31.5</v>
+        <v>33.53</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8917</v>
+        <v>0.9196</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>36</v>
+        <v>41.38</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9826</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>27.71</v>
+        <v>28.62</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8769</v>
+        <v>0.8967000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>28.77</v>
+        <v>29.79</v>
       </c>
       <c r="C66" t="n">
-        <v>0.8164</v>
+        <v>0.8381999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>31.69</v>
+        <v>33.24</v>
       </c>
       <c r="C67" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40.52</v>
+        <v>45.79</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9845</v>
+        <v>0.9913999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>24.43</v>
+        <v>25.46</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8203</v>
+        <v>0.8519</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>25.29</v>
+        <v>26.26</v>
       </c>
       <c r="C70" t="n">
-        <v>0.8244</v>
+        <v>0.8568</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>31.9</v>
+        <v>35.35</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9193</v>
+        <v>0.9404</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32.03</v>
+        <v>35.69</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8789</v>
+        <v>0.9175</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>28.86</v>
+        <v>29.98</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8375</v>
+        <v>0.8632</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>30.4</v>
+        <v>30.84</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8246</v>
+        <v>0.8393</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>28.97</v>
+        <v>29.75</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8499</v>
+        <v>0.8683999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>26.67</v>
+        <v>28.88</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8364</v>
+        <v>0.8792</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>33.5</v>
+        <v>34.73</v>
       </c>
       <c r="C77" t="n">
-        <v>0.9015</v>
+        <v>0.9162</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>26.68</v>
+        <v>27.07</v>
       </c>
       <c r="C78" t="n">
-        <v>0.7756</v>
+        <v>0.7968</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>33.02</v>
+        <v>34.71</v>
       </c>
       <c r="C79" t="n">
-        <v>0.9174</v>
+        <v>0.9363</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.53</v>
+        <v>39.19</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9568</v>
+        <v>0.9827</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>32.81</v>
+        <v>33.57</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9223</v>
+        <v>0.9336</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>38.47</v>
+        <v>40.73</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9658</v>
+        <v>0.9737</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>30.65</v>
+        <v>31.38</v>
       </c>
       <c r="C83" t="n">
-        <v>0.8374</v>
+        <v>0.8586</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>25.01</v>
+        <v>26.22</v>
       </c>
       <c r="C84" t="n">
-        <v>0.775</v>
+        <v>0.8198</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>23.91</v>
+        <v>25.43</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7983</v>
+        <v>0.8573</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>27.63</v>
+        <v>30.08</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8784</v>
+        <v>0.9294</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>27.87</v>
+        <v>29.01</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8241000000000001</v>
+        <v>0.8568</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>30.2</v>
+        <v>30.86</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8625</v>
+        <v>0.8821</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>34.42</v>
+        <v>36.09</v>
       </c>
       <c r="C89" t="n">
-        <v>0.9304</v>
+        <v>0.9464</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>29.79</v>
+        <v>30.16</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7762</v>
+        <v>0.792</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>29.22</v>
+        <v>30.76</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8743</v>
+        <v>0.9045</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>32.4</v>
+        <v>33.33</v>
       </c>
       <c r="C92" t="n">
-        <v>0.8764</v>
+        <v>0.8918</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>28.23</v>
+        <v>31.49</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8488</v>
+        <v>0.9076</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>35.82</v>
+        <v>37.82</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9646</v>
+        <v>0.9726</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>29.54</v>
+        <v>31.4</v>
       </c>
       <c r="C95" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.9203</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>28.65</v>
+        <v>33.08</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8973</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>23.8</v>
+        <v>23.83</v>
       </c>
       <c r="C97" t="n">
-        <v>0.6075</v>
+        <v>0.6234</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>29.5</v>
+        <v>30.01</v>
       </c>
       <c r="C98" t="n">
-        <v>0.77</v>
+        <v>0.7907</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>29.66</v>
+        <v>30.64</v>
       </c>
       <c r="C99" t="n">
-        <v>0.9109</v>
+        <v>0.9247</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>29.62</v>
+        <v>31.38</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8688</v>
+        <v>0.9029</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>27.98</v>
+        <v>30.07</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8679</v>
+        <v>0.9104</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>30.33</v>
+        <v>32.14</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8736</v>
+        <v>0.8995</v>
       </c>
     </row>
   </sheetData>
